--- a/artfynd/A 41623-2024 artfynd.xlsx
+++ b/artfynd/A 41623-2024 artfynd.xlsx
@@ -1049,7 +1049,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">

--- a/artfynd/A 41623-2024 artfynd.xlsx
+++ b/artfynd/A 41623-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101861257</v>
+        <v>105027858</v>
       </c>
       <c r="B2" t="n">
-        <v>41707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>215886</v>
+        <v>100945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ligusterfly</t>
+          <t>Skuggmalmätare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craniophora ligustri</t>
+          <t>Eupithecia immundata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Lienig &amp; Zeller, 1846)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -732,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503691.6696756685</v>
+        <v>503692</v>
       </c>
       <c r="R2" t="n">
-        <v>6628666.222374779</v>
+        <v>6628666</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,11 +775,16 @@
           <t>01:45</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mycket liten. Trolldruva växer i skogen</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
@@ -805,15 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101863640</v>
+        <v>101860034</v>
       </c>
       <c r="B3" t="n">
-        <v>40881</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,26 +816,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>215804</v>
+        <v>215785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Glimmalmätare</t>
+          <t>Brunflammig fältmätare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eupithecia venosata</t>
+          <t>Perizoma flavofasciata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Thunberg, 1792)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -862,10 +857,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503691.6696756685</v>
+        <v>503692</v>
       </c>
       <c r="R3" t="n">
-        <v>6628666.222374779</v>
+        <v>6628666</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -935,42 +930,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105027858</v>
+        <v>101863640</v>
       </c>
       <c r="B4" t="n">
-        <v>40848</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>41579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100945</v>
+        <v>215804</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skuggmalmätare</t>
+          <t>Glimmalmätare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eupithecia immundata</t>
+          <t>Eupithecia venosata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lienig &amp; Zeller, 1846)</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -992,10 +982,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503691.6696756685</v>
+        <v>503692</v>
       </c>
       <c r="R4" t="n">
-        <v>6628666.222374779</v>
+        <v>6628666</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1040,16 +1030,11 @@
           <t>01:45</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Mycket liten. Trolldruva växer i skogen</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
@@ -1070,15 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101860034</v>
+        <v>102019872</v>
       </c>
       <c r="B5" t="n">
-        <v>40952</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>41570</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,26 +1066,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>215785</v>
+        <v>215827</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunflammig fältmätare</t>
+          <t>Brunbandad malmätare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perizoma flavofasciata</t>
+          <t>Eupithecia sinuosaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Thunberg, 1792)</t>
+          <t>Eversmann, 1848</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1127,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503691.6696756685</v>
+        <v>503692</v>
       </c>
       <c r="R5" t="n">
-        <v>6628666.222374779</v>
+        <v>6628666</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1157,17 +1137,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-24</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-25</t>
+          <t>2022-07-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1197,6 +1177,117 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132801623</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101974</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Korsning  av gamla vägar, öster om Rällen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>503692</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6628666</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Längs bägge vägar</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Stefan Risberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Stefan Risberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41623-2024 artfynd.xlsx
+++ b/artfynd/A 41623-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105027858</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -927,6 +937,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101860034</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1052,6 +1067,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101863640</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1177,6 +1197,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102019872</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1288,8 +1313,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132801623</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>